--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
     <t xml:space="preserve">Constitución</t>
   </si>
   <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -998,7 +998,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7102</v>
+        <v>7110</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2024</v>
@@ -1015,7 +1015,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7110</v>
+        <v>7102</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:31</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -998,7 +998,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7110</v>
+        <v>7102</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2024</v>
@@ -1015,7 +1015,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7102</v>
+        <v>7110</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:14</t>
+    <t xml:space="preserve">2026-10-05 08:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
